--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential ELSS Tax Saver Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential ELSS Tax Saver Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="231">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential ELSS Tax Saver Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,6 +76,30 @@
     <t>INE040A01034</t>
   </si>
   <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -85,15 +109,6 @@
     <t>Automobiles</t>
   </si>
   <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
     <t>Bharti Airtel Ltd.</t>
   </si>
   <si>
@@ -103,21 +118,6 @@
     <t>Telecom - Services</t>
   </si>
   <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Larsen &amp; Toubro Ltd.</t>
   </si>
   <si>
@@ -127,6 +127,39 @@
     <t>Construction</t>
   </si>
   <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -136,22 +169,19 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
   </si>
   <si>
     <t>SBI Cards &amp; Payment Services Ltd.</t>
@@ -163,21 +193,6 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>Syngene International Ltd.</t>
   </si>
   <si>
@@ -187,19 +202,25 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
   </si>
   <si>
     <t>Max Financial Services Ltd.</t>
@@ -208,10 +229,13 @@
     <t>INE180A01020</t>
   </si>
   <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
   </si>
   <si>
     <t>PVR INOX Ltd.</t>
@@ -223,15 +247,6 @@
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
     <t>Inox Wind Ltd.</t>
   </si>
   <si>
@@ -241,10 +256,10 @@
     <t>Electrical Equipment</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
   </si>
   <si>
     <t>Wockhardt Ltd.</t>
@@ -253,6 +268,174 @@
     <t>INE049B01025</t>
   </si>
   <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Mahindra Lifespace Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE813A01018</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>V-Mart Retail Ltd.</t>
+  </si>
+  <si>
+    <t>INE665J01013</t>
+  </si>
+  <si>
+    <t>Chalet Hotels Ltd.</t>
+  </si>
+  <si>
+    <t>INE427F01016</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>PDS Ltd</t>
+  </si>
+  <si>
+    <t>INE111Q01021</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Arvind Fashions Ltd.</t>
+  </si>
+  <si>
+    <t>INE955V01021</t>
+  </si>
+  <si>
+    <t>TBO Tek Ltd.</t>
+  </si>
+  <si>
+    <t>INE673O01025</t>
+  </si>
+  <si>
+    <t>Shilpa Medicare Ltd.</t>
+  </si>
+  <si>
+    <t>INE790G01031</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>Sapphire Foods India Ltd</t>
+  </si>
+  <si>
+    <t>INE806T01020</t>
+  </si>
+  <si>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
+  </si>
+  <si>
+    <t>Schloss Bangalore Ltd.</t>
+  </si>
+  <si>
+    <t>INE0AQ201015</t>
+  </si>
+  <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Godavari Biorefineries Ltd</t>
+  </si>
+  <si>
+    <t>INE497S01012</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Sundram Fasteners Ltd.</t>
+  </si>
+  <si>
+    <t>INE387A01021</t>
+  </si>
+  <si>
     <t>United Breweries Ltd.</t>
   </si>
   <si>
@@ -262,28 +445,133 @@
     <t>Beverages</t>
   </si>
   <si>
-    <t>Mahindra Lifespace Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE813A01018</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Updater Services Ltd</t>
+  </si>
+  <si>
+    <t>INE851I01011</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Brainbees Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE02RE01045</t>
+  </si>
+  <si>
+    <t>Techno Electric &amp; Engineering Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE285K01026</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>Power Mech Projects Ltd</t>
+  </si>
+  <si>
+    <t>INE211R01019</t>
+  </si>
+  <si>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Apollo Tyres Ltd.</t>
+  </si>
+  <si>
+    <t>INE438A01022</t>
+  </si>
+  <si>
+    <t>Red Tape Ltd</t>
+  </si>
+  <si>
+    <t>INE0LXT01019</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Teamlease Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE985S01024</t>
+  </si>
+  <si>
+    <t>International Gemmological Institute (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE0Q9301021</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd.</t>
+  </si>
+  <si>
+    <t>INE073K01018</t>
+  </si>
+  <si>
+    <t>Brigade Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE791I01019</t>
+  </si>
+  <si>
+    <t>Varroc Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE665L01035</t>
+  </si>
+  <si>
+    <t>INOX India Ltd</t>
+  </si>
+  <si>
+    <t>INE616N01034</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Tech Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
+  </si>
+  <si>
+    <t>PNC Infratech Ltd.</t>
+  </si>
+  <si>
+    <t>INE195J01029</t>
+  </si>
+  <si>
+    <t>Mahindra Lifespace Developers Ltd (Right Share)</t>
+  </si>
+  <si>
+    <t>INE813A20018</t>
   </si>
   <si>
     <t>Krishna Institute of Medical Sciences</t>
@@ -292,283 +580,16 @@
     <t>INE967H01025</t>
   </si>
   <si>
-    <t>V-Mart Retail Ltd.</t>
-  </si>
-  <si>
-    <t>INE665J01013</t>
-  </si>
-  <si>
-    <t>PDS Ltd</t>
-  </si>
-  <si>
-    <t>INE111Q01021</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>Arvind Fashions Ltd.</t>
-  </si>
-  <si>
-    <t>INE955V01021</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Bajaj Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE296A01024</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Chalet Hotels Ltd.</t>
-  </si>
-  <si>
-    <t>INE427F01016</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>TBO Tek Ltd.</t>
-  </si>
-  <si>
-    <t>INE673O01025</t>
-  </si>
-  <si>
-    <t>Shilpa Medicare Ltd.</t>
-  </si>
-  <si>
-    <t>INE790G01031</t>
-  </si>
-  <si>
-    <t>Sapphire Foods India Ltd</t>
-  </si>
-  <si>
-    <t>INE806T01020</t>
-  </si>
-  <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Hyundai Motor India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0V6F01027</t>
-  </si>
-  <si>
-    <t>Cartrade Tech Ltd</t>
-  </si>
-  <si>
-    <t>INE290S01011</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd</t>
-  </si>
-  <si>
-    <t>INE634S01028</t>
-  </si>
-  <si>
-    <t>Sundram Fasteners Ltd.</t>
-  </si>
-  <si>
-    <t>INE387A01021</t>
-  </si>
-  <si>
-    <t>Godavari Biorefineries Ltd</t>
-  </si>
-  <si>
-    <t>INE497S01012</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Brainbees Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE02RE01045</t>
-  </si>
-  <si>
-    <t>Updater Services Ltd</t>
-  </si>
-  <si>
-    <t>INE851I01011</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Red Tape Ltd</t>
-  </si>
-  <si>
-    <t>INE0LXT01019</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Power Mech Projects Ltd</t>
-  </si>
-  <si>
-    <t>INE211R01019</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Techno Electric &amp; Engineering Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE285K01026</t>
-  </si>
-  <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
-    <t>Brigade Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE791I01019</t>
-  </si>
-  <si>
-    <t>Quess Corp Ltd.</t>
-  </si>
-  <si>
-    <t>INE615P01015</t>
-  </si>
-  <si>
-    <t>Varroc Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE665L01035</t>
-  </si>
-  <si>
-    <t>Tech Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE669C01036</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>PNC Infratech Ltd.</t>
-  </si>
-  <si>
-    <t>INE195J01029</t>
-  </si>
-  <si>
-    <t>Navin Fluorine International Ltd.</t>
-  </si>
-  <si>
-    <t>INE048G01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
+    <t>Greenpanel Industries Ltd</t>
+  </si>
+  <si>
+    <t>INE08ZM01014</t>
+  </si>
+  <si>
+    <t>Barbeque Nation Hospitality</t>
+  </si>
+  <si>
+    <t>INE382M01027</t>
   </si>
   <si>
     <t>Ganesha Ecosphere Ltd</t>
@@ -577,43 +598,16 @@
     <t>INE845D01014</t>
   </si>
   <si>
-    <t>Teamlease Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE985S01024</t>
-  </si>
-  <si>
-    <t>INOX India Ltd</t>
-  </si>
-  <si>
-    <t>INE616N01034</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>International Gemmological Institute (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q9301021</t>
-  </si>
-  <si>
-    <t>Barbeque Nation Hospitality</t>
-  </si>
-  <si>
-    <t>INE382M01027</t>
-  </si>
-  <si>
     <t>Rolex Rings Ltd.</t>
   </si>
   <si>
     <t>INE645S01016</t>
   </si>
   <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
   </si>
   <si>
     <t>Samhi hotels Ltd</t>
@@ -628,10 +622,10 @@
     <t>INE742B01025</t>
   </si>
   <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
+    <t>Godawari Power And Ispat Ltd.</t>
+  </si>
+  <si>
+    <t>INE177H01039</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -667,6 +661,15 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>91 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002025X042</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
@@ -691,7 +694,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1074,13 +1077,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1098,7 +1101,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="25412700"/>
+          <a:off x="666750" y="25603200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1113,13 +1116,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>146</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>157</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1137,7 +1140,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="28270200"/>
+          <a:off x="666750" y="28460700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1471,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J145"/>
+  <dimension ref="B1:J146"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1571,10 +1574,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1339664.5200000007</v>
+        <v>1384920.15</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9887738691917001</v>
+        <v>0.9641662470350003</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1608,10 +1611,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1339664.5200000007</v>
+        <v>1384920.15</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9887738691917001</v>
+        <v>0.9641662470350003</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1634,13 +1637,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>9918908</v>
+        <v>9252413</v>
       </c>
       <c r="G8" s="15">
-        <v>124264.08</v>
+        <v>133771.39</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0917163016183</v>
+        <v>0.0931301772578</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1663,13 +1666,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>6147320</v>
+        <v>5173934</v>
       </c>
       <c r="G9" s="15">
-        <v>104427.60</v>
+        <v>100627.84</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0770754771521</v>
+        <v>0.0700560005863</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1692,13 +1695,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>612703</v>
+        <v>4810866</v>
       </c>
       <c r="G10" s="15">
-        <v>75427.72</v>
+        <v>80707.09</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0556713695373</v>
+        <v>0.0561873925184</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1718,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>1958000</v>
+        <v>6002223</v>
       </c>
       <c r="G11" s="15">
-        <v>71753.85</v>
+        <v>71558.50</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0529597752534</v>
+        <v>0.0498182443144</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1738,25 +1741,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="F12" s="14">
-        <v>4284654</v>
+        <v>1722278</v>
       </c>
       <c r="G12" s="15">
-        <v>69681.33</v>
+        <v>68927.29</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0514300985405</v>
+        <v>0.0479864247176</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1767,25 +1770,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F13" s="14">
-        <v>3672417</v>
+        <v>545897</v>
       </c>
       <c r="G13" s="15">
-        <v>64045.12</v>
+        <v>67249.05</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0472701487276</v>
+        <v>0.0468180524021</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1796,25 +1799,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F14" s="14">
-        <v>5558385</v>
+        <v>3589160</v>
       </c>
       <c r="G14" s="15">
-        <v>54811.23</v>
+        <v>66621.99</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0404548386207</v>
+        <v>0.0463815000948</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1837,13 +1840,13 @@
         <v>36</v>
       </c>
       <c r="F15" s="14">
-        <v>1535066</v>
+        <v>1638689</v>
       </c>
       <c r="G15" s="15">
-        <v>54761.94</v>
+        <v>60223.46</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0404184588679</v>
+        <v>0.0419269135566</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1866,13 +1869,13 @@
         <v>39</v>
       </c>
       <c r="F16" s="14">
-        <v>2731994</v>
+        <v>15784132</v>
       </c>
       <c r="G16" s="15">
-        <v>51356.02</v>
+        <v>52703.22</v>
       </c>
       <c r="H16" s="16">
-        <v>0.037904631976</v>
+        <v>0.0366914047963</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1895,13 +1898,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>3650000</v>
+        <v>3614294</v>
       </c>
       <c r="G17" s="15">
-        <v>46176.15</v>
+        <v>51355.50</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0340814956419</v>
+        <v>0.0357531368864</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1921,16 +1924,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F18" s="14">
-        <v>13114273</v>
+        <v>1567366</v>
       </c>
       <c r="G18" s="15">
-        <v>42490.24</v>
+        <v>43585.31</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0313610149262</v>
+        <v>0.0303436156725</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1941,25 +1944,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="F19" s="14">
-        <v>5090124</v>
+        <v>1810881</v>
       </c>
       <c r="G19" s="15">
-        <v>39611.34</v>
+        <v>32816.79</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0292361687057</v>
+        <v>0.0228466899367</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1970,25 +1973,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>22</v>
-      </c>
       <c r="F20" s="14">
-        <v>1452731</v>
+        <v>2028207</v>
       </c>
       <c r="G20" s="15">
-        <v>35706.68</v>
+        <v>31694.79</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0263542339239</v>
+        <v>0.0220655658197</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2008,16 +2011,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F21" s="14">
-        <v>2114122</v>
+        <v>520762</v>
       </c>
       <c r="G21" s="15">
-        <v>31365.11</v>
+        <v>26551.05</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0231498264748</v>
+        <v>0.0184845503428</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2028,25 +2031,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="F22" s="14">
-        <v>3580555</v>
+        <v>233144</v>
       </c>
       <c r="G22" s="15">
-        <v>26734.21</v>
+        <v>26135.44</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0197318715745</v>
+        <v>0.0181952072106</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2057,25 +2060,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" s="14">
-        <v>442922</v>
+        <v>2811025</v>
       </c>
       <c r="G23" s="15">
-        <v>22425.36</v>
+        <v>25890.95</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0165516139632</v>
+        <v>0.0180249959492</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2098,13 +2101,13 @@
         <v>61</v>
       </c>
       <c r="F24" s="14">
-        <v>190075</v>
+        <v>3721293</v>
       </c>
       <c r="G24" s="15">
-        <v>21834.77</v>
+        <v>24060.02</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0161157138175</v>
+        <v>0.0167503225273</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2124,16 +2127,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F25" s="14">
-        <v>1838139</v>
+        <v>2762317</v>
       </c>
       <c r="G25" s="15">
-        <v>20509.04</v>
+        <v>22438.30</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0151372246794</v>
+        <v>0.015621298817</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2153,16 +2156,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F26" s="14">
-        <v>2512596</v>
+        <v>9187913</v>
       </c>
       <c r="G26" s="15">
-        <v>19419.85</v>
+        <v>21895.72</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0143333199745</v>
+        <v>0.0152435605609</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2185,13 +2188,13 @@
         <v>68</v>
       </c>
       <c r="F27" s="14">
-        <v>1775000</v>
+        <v>397202</v>
       </c>
       <c r="G27" s="15">
-        <v>19356.38</v>
+        <v>21170.87</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0142864743079</v>
+        <v>0.0147389279262</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2211,16 +2214,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F28" s="14">
-        <v>6731337</v>
+        <v>1249752</v>
       </c>
       <c r="G28" s="15">
-        <v>17677.16</v>
+        <v>18780.02</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0130470827797</v>
+        <v>0.01307444433</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2231,25 +2234,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="F29" s="14">
-        <v>9015147</v>
+        <v>7311823</v>
       </c>
       <c r="G29" s="15">
-        <v>15198.64</v>
+        <v>17504.50</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0112177473202</v>
+        <v>0.0121864412697</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2260,25 +2263,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="F30" s="14">
-        <v>6350404</v>
+        <v>1775000</v>
       </c>
       <c r="G30" s="15">
-        <v>13993.12</v>
+        <v>17488.19</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0103279822656</v>
+        <v>0.0121750864263</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2298,16 +2301,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="F31" s="14">
-        <v>973753</v>
+        <v>8641424</v>
       </c>
       <c r="G31" s="15">
-        <v>13797.11</v>
+        <v>16850.78</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0101833120417</v>
+        <v>0.0117313285623</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2318,25 +2321,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F32" s="14">
-        <v>592115</v>
+        <v>2420336</v>
       </c>
       <c r="G32" s="15">
-        <v>12706.79</v>
+        <v>13396.56</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0093785733112</v>
+        <v>0.0093265384133</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2356,16 +2359,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
-        <v>2925710</v>
+        <v>830105</v>
       </c>
       <c r="G33" s="15">
-        <v>12233.86</v>
+        <v>12163.53</v>
       </c>
       <c r="H33" s="16">
-        <v>0.009029515156</v>
+        <v>0.0084681164259</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2376,25 +2379,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>86</v>
-      </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F34" s="14">
-        <v>279868</v>
+        <v>640499</v>
       </c>
       <c r="G34" s="15">
-        <v>12102.47</v>
+        <v>12011.92</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0089325393858</v>
+        <v>0.0083625672036</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2405,25 +2408,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="F35" s="14">
-        <v>640499</v>
+        <v>3172896</v>
       </c>
       <c r="G35" s="15">
-        <v>11903.67</v>
+        <v>11006.78</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0087858099306</v>
+        <v>0.0076627997394</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2434,25 +2437,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>91</v>
-      </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F36" s="14">
-        <v>1932346</v>
+        <v>2220337</v>
       </c>
       <c r="G36" s="15">
-        <v>11771.85</v>
+        <v>10605.44</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0086885167878</v>
+        <v>0.0073833912251</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2463,25 +2466,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F37" s="14">
-        <v>348299</v>
+        <v>294520</v>
       </c>
       <c r="G37" s="15">
-        <v>11181.09</v>
+        <v>10200.41</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0082524911693</v>
+        <v>0.0071014137731</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2492,25 +2495,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="F38" s="14">
-        <v>2151197</v>
+        <v>6646834</v>
       </c>
       <c r="G38" s="15">
-        <v>10687.15</v>
+        <v>10177.63</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0078879260429</v>
+        <v>0.0070855545865</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2521,25 +2524,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F39" s="14">
-        <v>2110986</v>
+        <v>298986</v>
       </c>
       <c r="G39" s="15">
-        <v>10177.06</v>
+        <v>10175.09</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0075114409936</v>
+        <v>0.0070837862663</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2550,25 +2553,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="D40" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="F40" s="14">
-        <v>2234765</v>
+        <v>1102838</v>
       </c>
       <c r="G40" s="15">
-        <v>10000.57</v>
+        <v>10120.74</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0073811780079</v>
+        <v>0.0070459483913</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2579,25 +2582,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="D41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="F41" s="14">
-        <v>2220337</v>
+        <v>2272348</v>
       </c>
       <c r="G41" s="15">
-        <v>9619.61</v>
+        <v>9969.93</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0071000006776</v>
+        <v>0.0069409561203</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2617,16 +2620,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F42" s="14">
-        <v>546842</v>
+        <v>2103045</v>
       </c>
       <c r="G42" s="15">
-        <v>9435.49</v>
+        <v>9683.47</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0069641061741</v>
+        <v>0.0067415258043</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2646,16 +2649,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="F43" s="14">
-        <v>1720974</v>
+        <v>715837</v>
       </c>
       <c r="G43" s="15">
-        <v>8825.15</v>
+        <v>9339.53</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0065136290328</v>
+        <v>0.0065020785416</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2675,16 +2678,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="F44" s="14">
-        <v>6193188</v>
+        <v>1032968</v>
       </c>
       <c r="G44" s="15">
-        <v>8748.50</v>
+        <v>9311.17</v>
       </c>
       <c r="H44" s="16">
-        <v>0.006457055528</v>
+        <v>0.0064823346201</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2695,25 +2698,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F45" s="14">
-        <v>108424</v>
+        <v>546842</v>
       </c>
       <c r="G45" s="15">
-        <v>8549.34</v>
+        <v>8949.62</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0063100603656</v>
+        <v>0.0062306274681</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2724,25 +2727,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="D46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="F46" s="14">
-        <v>3198403</v>
+        <v>2134358</v>
       </c>
       <c r="G46" s="15">
-        <v>8351.03</v>
+        <v>8922.68</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0061636925675</v>
+        <v>0.0062118721351</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2762,16 +2765,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="F47" s="14">
-        <v>1051557</v>
+        <v>943260</v>
       </c>
       <c r="G47" s="15">
-        <v>8106.98</v>
+        <v>8772.32</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0059835651854</v>
+        <v>0.0061071931491</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2782,25 +2785,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>119</v>
-      </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F48" s="14">
-        <v>501330</v>
+        <v>2287726</v>
       </c>
       <c r="G48" s="15">
-        <v>7811.22</v>
+        <v>7277.26</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0057652719074</v>
+        <v>0.0050663487443</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2811,25 +2814,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>121</v>
-      </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49" s="14">
-        <v>1032968</v>
+        <v>384114</v>
       </c>
       <c r="G49" s="15">
-        <v>7330.97</v>
+        <v>7095.35</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0054108110378</v>
+        <v>0.0049397049937</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2840,25 +2843,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>123</v>
-      </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F50" s="14">
-        <v>2287726</v>
+        <v>1552569</v>
       </c>
       <c r="G50" s="15">
-        <v>6625.25</v>
+        <v>6753.68</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0048899362333</v>
+        <v>0.0047018380801</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2869,25 +2872,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F51" s="14">
         <v>264365</v>
       </c>
       <c r="G51" s="15">
-        <v>6526.64</v>
+        <v>6208.08</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0048171545855</v>
+        <v>0.0043219973331</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2898,25 +2901,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>127</v>
-      </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F52" s="14">
-        <v>384114</v>
+        <v>753213</v>
       </c>
       <c r="G52" s="15">
-        <v>6443.70</v>
+        <v>6153.37</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0047559385844</v>
+        <v>0.00428390883</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2927,25 +2930,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F53" s="14">
-        <v>340000</v>
+        <v>500929</v>
       </c>
       <c r="G53" s="15">
-        <v>5614.76</v>
+        <v>5749.66</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0041441180884</v>
+        <v>0.0040028503476</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2956,25 +2959,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="F54" s="14">
-        <v>225459</v>
+        <v>1995279</v>
       </c>
       <c r="G54" s="15">
-        <v>5490.83</v>
+        <v>5689.94</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0040526483631</v>
+        <v>0.0039612739374</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2985,25 +2988,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="D55" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="F55" s="14">
-        <v>501302</v>
+        <v>138600</v>
       </c>
       <c r="G55" s="15">
-        <v>5234.6</v>
+        <v>5299.65</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0038635312187</v>
+        <v>0.0036895583121</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3023,16 +3026,16 @@
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F56" s="14">
-        <v>1995279</v>
+        <v>98000</v>
       </c>
       <c r="G56" s="15">
-        <v>4904.4</v>
+        <v>5226.83</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0036198186125</v>
+        <v>0.0036388618253</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3052,16 +3055,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F57" s="14">
-        <v>453213</v>
+        <v>1621036</v>
       </c>
       <c r="G57" s="15">
-        <v>4492.25</v>
+        <v>5161.38</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0033156207002</v>
+        <v>0.0035932962518</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3081,16 +3084,16 @@
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="F58" s="14">
-        <v>78000</v>
+        <v>501302</v>
       </c>
       <c r="G58" s="15">
-        <v>4051.55</v>
+        <v>5145.87</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0029903507258</v>
+        <v>0.0035824983596</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3110,16 +3113,16 @@
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="F59" s="14">
-        <v>2375359</v>
+        <v>207315</v>
       </c>
       <c r="G59" s="15">
-        <v>4011.98</v>
+        <v>4098.20</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0029611450691</v>
+        <v>0.002853121975</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3130,25 +3133,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F60" s="14">
-        <v>338676</v>
+        <v>200000</v>
       </c>
       <c r="G60" s="15">
-        <v>3968.94</v>
+        <v>3915.40</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0029293782897</v>
+        <v>0.0027258586162</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3159,25 +3162,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F61" s="14">
-        <v>752629</v>
+        <v>128414</v>
       </c>
       <c r="G61" s="15">
-        <v>3596.81</v>
+        <v>3822.63</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0026547181681</v>
+        <v>0.0026612731578</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3188,25 +3191,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F62" s="14">
-        <v>1055299</v>
+        <v>1060309</v>
       </c>
       <c r="G62" s="15">
-        <v>3589.60</v>
+        <v>3462.44</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0026493966421</v>
+        <v>0.0024105128229</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3217,25 +3220,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F63" s="14">
-        <v>179045</v>
+        <v>1608337</v>
       </c>
       <c r="G63" s="15">
-        <v>3108.40</v>
+        <v>3269.11</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0022942346006</v>
+        <v>0.0022759185934</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3246,25 +3249,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F64" s="14">
-        <v>1000000</v>
+        <v>847165</v>
       </c>
       <c r="G64" s="15">
-        <v>3016.50</v>
+        <v>2951.95</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0022264054409</v>
+        <v>0.0020551152735</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3275,25 +3278,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F65" s="14">
-        <v>281226</v>
+        <v>186977</v>
       </c>
       <c r="G65" s="15">
-        <v>2728.60</v>
+        <v>2636</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0020139134381</v>
+        <v>0.0018351543424</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3304,25 +3307,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="F66" s="14">
-        <v>395575</v>
+        <v>4480844</v>
       </c>
       <c r="G66" s="15">
-        <v>2669.54</v>
+        <v>2593.51</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0019703226855</v>
+        <v>0.0018055732695</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3345,13 +3348,13 @@
         <v>36</v>
       </c>
       <c r="F67" s="14">
-        <v>108109</v>
+        <v>78313</v>
       </c>
       <c r="G67" s="15">
-        <v>2328.67</v>
+        <v>2433.34</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0017187348112</v>
+        <v>0.001694064669</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3371,16 +3374,16 @@
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="F68" s="14">
-        <v>3801022</v>
+        <v>113372</v>
       </c>
       <c r="G68" s="15">
-        <v>2133.51</v>
+        <v>2287.17</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0015746919517</v>
+        <v>0.0015923027152</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3400,16 +3403,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="F69" s="14">
-        <v>58238</v>
+        <v>452267</v>
       </c>
       <c r="G69" s="15">
-        <v>2028.87</v>
+        <v>2128.14</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0014974597072</v>
+        <v>0.0014815877702</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3420,25 +3423,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="D70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="F70" s="14">
-        <v>186977</v>
+        <v>1582300</v>
       </c>
       <c r="G70" s="15">
-        <v>2015.14</v>
+        <v>2122.66</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0014873259275</v>
+        <v>0.0014777726542</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3458,16 +3461,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="F71" s="14">
-        <v>407766</v>
+        <v>98841</v>
       </c>
       <c r="G71" s="15">
-        <v>1783.16</v>
+        <v>1933.03</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0013161071195</v>
+        <v>0.0013457543241</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3487,16 +3490,16 @@
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="F72" s="14">
-        <v>140644</v>
+        <v>440701</v>
       </c>
       <c r="G72" s="15">
-        <v>1647.01</v>
+        <v>1713.89</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0012156181088</v>
+        <v>0.0011931914552</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3516,16 +3519,16 @@
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="F73" s="14">
-        <v>272627</v>
+        <v>293393</v>
       </c>
       <c r="G73" s="15">
-        <v>1624.31</v>
+        <v>1595.91</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0011988637897</v>
+        <v>0.0011110550708</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3545,16 +3548,16 @@
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F74" s="14">
-        <v>276300</v>
+        <v>140644</v>
       </c>
       <c r="G74" s="15">
-        <v>1534.98</v>
+        <v>1539.21</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0011329314847</v>
+        <v>0.0010715811515</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3574,16 +3577,16 @@
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="F75" s="14">
-        <v>85000</v>
+        <v>276300</v>
       </c>
       <c r="G75" s="15">
-        <v>1423.28</v>
+        <v>1460.66</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0010504884256</v>
+        <v>0.0010168955014</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3606,13 +3609,13 @@
         <v>179</v>
       </c>
       <c r="F76" s="14">
-        <v>138041</v>
+        <v>121242</v>
       </c>
       <c r="G76" s="15">
-        <v>1304.49</v>
+        <v>1447.57</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0009628124096</v>
+        <v>0.0010077823867</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3632,16 +3635,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F77" s="14">
-        <v>400000</v>
+        <v>85000</v>
       </c>
       <c r="G77" s="15">
-        <v>1276</v>
+        <v>1337.82</v>
       </c>
       <c r="H77" s="16">
-        <v>0.000941784632</v>
+        <v>0.0009313756382</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3661,16 +3664,16 @@
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="F78" s="14">
-        <v>30000</v>
+        <v>400000</v>
       </c>
       <c r="G78" s="15">
-        <v>1244.61</v>
+        <v>1167.80</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0009186164349</v>
+        <v>0.0008130095755</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3681,25 +3684,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C79" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F79" s="14">
-        <v>70883</v>
+        <v>1189836</v>
       </c>
       <c r="G79" s="15">
-        <v>1223.76</v>
+        <v>1069.66</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0009032275559</v>
+        <v>0.0007446855819</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3710,25 +3713,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F80" s="14">
-        <v>48841</v>
+        <v>128658</v>
       </c>
       <c r="G80" s="15">
-        <v>1192.77</v>
+        <v>880.34</v>
       </c>
       <c r="H80" s="16">
-        <v>0.000880354589</v>
+        <v>0.0006128830704</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3739,25 +3742,25 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>190</v>
-      </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="F81" s="14">
-        <v>121242</v>
+        <v>293067</v>
       </c>
       <c r="G81" s="15">
-        <v>1111.18</v>
+        <v>747.73</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0008201349901</v>
+        <v>0.0005205614402</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -3768,25 +3771,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="F82" s="14">
-        <v>193415</v>
+        <v>230000</v>
       </c>
       <c r="G82" s="15">
-        <v>979.84</v>
+        <v>692.65</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0007231961237</v>
+        <v>0.0004822153472</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3797,25 +3800,25 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F83" s="14">
-        <v>230000</v>
+        <v>35883</v>
       </c>
       <c r="G83" s="15">
-        <v>746.12</v>
+        <v>550.55</v>
       </c>
       <c r="H83" s="16">
-        <v>0.000550693064</v>
+        <v>0.0003832868828</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -3826,25 +3829,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F84" s="14">
-        <v>24046</v>
+        <v>32521</v>
       </c>
       <c r="G84" s="15">
-        <v>432.42</v>
+        <v>521.28</v>
       </c>
       <c r="H84" s="16">
-        <v>0.0003191587073</v>
+        <v>0.0003629094292</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -3855,25 +3858,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="F85" s="14">
-        <v>279460</v>
+        <v>194368</v>
       </c>
       <c r="G85" s="15">
-        <v>376.21</v>
+        <v>485.05</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0002776714705</v>
+        <v>0.0003376864999</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -3884,25 +3887,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F86" s="14">
         <v>186214</v>
       </c>
       <c r="G86" s="15">
-        <v>318.46</v>
+        <v>358.41</v>
       </c>
       <c r="H86" s="16">
-        <v>0.0002350475971</v>
+        <v>0.0002495211183</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -3913,25 +3916,25 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F87" s="14">
-        <v>66906</v>
+        <v>74008</v>
       </c>
       <c r="G87" s="15">
-        <v>301.11</v>
+        <v>289.37</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0002222419832</v>
+        <v>0.0002014562261</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -3942,25 +3945,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="F88" s="14">
-        <v>121156</v>
+        <v>122177</v>
       </c>
       <c r="G88" s="15">
-        <v>197.42</v>
+        <v>232.72</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0001457109107</v>
+        <v>0.0001620171163</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -3979,7 +3982,7 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>13</v>
@@ -3994,10 +3997,10 @@
         <v>13</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>13</v>
@@ -4016,7 +4019,7 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>13</v>
@@ -4031,10 +4034,10 @@
         <v>13</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>13</v>
@@ -4068,10 +4071,10 @@
         <v>13</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I94" s="9" t="s">
         <v>13</v>
@@ -4090,7 +4093,7 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>13</v>
@@ -4105,10 +4108,10 @@
         <v>13</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I96" s="9" t="s">
         <v>13</v>
@@ -4127,7 +4130,7 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>13</v>
@@ -4142,10 +4145,10 @@
         <v>13</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I98" s="9" t="s">
         <v>13</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>13</v>
@@ -4179,10 +4182,10 @@
         <v>13</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I100" s="9" t="s">
         <v>13</v>
@@ -4201,7 +4204,7 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>13</v>
@@ -4216,10 +4219,10 @@
         <v>13</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I102" s="9" t="s">
         <v>13</v>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>13</v>
@@ -4252,11 +4255,11 @@
       <c r="F104" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>207</v>
+      <c r="G104" s="9">
+        <v>396.77</v>
+      </c>
+      <c r="H104" s="10">
+        <v>0.0002762269303</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>13</v>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>13</v>
@@ -4290,10 +4293,10 @@
         <v>13</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>13</v>
@@ -4312,7 +4315,7 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>13</v>
@@ -4327,10 +4330,10 @@
         <v>13</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>13</v>
@@ -4349,7 +4352,7 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>13</v>
@@ -4363,11 +4366,11 @@
       <c r="F110" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G110" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>207</v>
+      <c r="G110" s="9">
+        <v>396.77</v>
+      </c>
+      <c r="H110" s="10">
+        <v>0.0002762269303</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>13</v>
@@ -4378,35 +4381,35 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>13</v>
+        <v>215</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F111" s="14">
+        <v>400000</v>
+      </c>
+      <c r="G111" s="15">
+        <v>396.77</v>
+      </c>
+      <c r="H111" s="16">
+        <v>0.0002762269303</v>
+      </c>
+      <c r="I111" s="15">
+        <v>5.61</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I112" s="9" t="s">
+      <c r="B112" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4414,7 +4417,28 @@
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I113" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4422,28 +4446,7 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H114" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I114" s="9" t="s">
+      <c r="B114" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J114" s="11" t="s">
@@ -4451,7 +4454,28 @@
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I115" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4459,28 +4483,7 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="9">
-        <v>16085.09</v>
-      </c>
-      <c r="H116" s="10">
-        <v>0.0118720145515</v>
-      </c>
-      <c r="I116" s="9" t="s">
+      <c r="B116" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
@@ -4488,7 +4491,28 @@
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="9">
+        <v>53172.33</v>
+      </c>
+      <c r="H117" s="10">
+        <v>0.0370179940427</v>
+      </c>
+      <c r="I117" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
@@ -4496,31 +4520,10 @@
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="C118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="18">
-        <v>-875.0914317208808</v>
-      </c>
-      <c r="H118" s="19">
-        <v>-0.0006458837477035183</v>
-      </c>
-      <c r="I118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="20" t="s">
+      <c r="B118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4541,10 +4544,10 @@
         <v>13</v>
       </c>
       <c r="G119" s="18">
-        <v>1354874.51856828</v>
+        <v>-2097.803760199342</v>
       </c>
       <c r="H119" s="19">
-        <v>0.9999999999954965</v>
+        <v>-0.001460468012178013</v>
       </c>
       <c r="I119" s="18" t="s">
         <v>13</v>
@@ -4553,19 +4556,36 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="2:9" ht="15" customHeight="1">
-      <c r="B122" s="13" t="s">
+    <row r="120" spans="2:10" ht="15" customHeight="1">
+      <c r="B120" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="21"/>
-      <c r="G122" s="21"/>
-      <c r="H122" s="21"/>
-      <c r="I122" s="21"/>
-    </row>
-    <row r="123" spans="2:8" ht="15" customHeight="1">
+      <c r="C120" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="18">
+        <v>1436391.4462398</v>
+      </c>
+      <c r="H120" s="19">
+        <v>0.9999999999958221</v>
+      </c>
+      <c r="I120" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" ht="15" customHeight="1">
       <c r="B123" s="13" t="s">
         <v>223</v>
       </c>
@@ -4575,9 +4595,10 @@
       <c r="F123" s="21"/>
       <c r="G123" s="21"/>
       <c r="H123" s="21"/>
-    </row>
-    <row r="124" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B124" s="22" t="s">
+      <c r="I123" s="21"/>
+    </row>
+    <row r="124" spans="2:8" ht="15" customHeight="1">
+      <c r="B124" s="13" t="s">
         <v>224</v>
       </c>
       <c r="C124" s="21"/>
@@ -4609,13 +4630,19 @@
       <c r="G126" s="21"/>
       <c r="H126" s="21"/>
     </row>
-    <row r="129" ht="15">
-      <c r="B129" s="21" t="s">
+    <row r="127" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B127" s="22" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="144" ht="15">
-      <c r="B144" s="21" t="s">
+      <c r="C127" s="21"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="21"/>
+    </row>
+    <row r="130" ht="15">
+      <c r="B130" s="21" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4624,16 +4651,21 @@
         <v>229</v>
       </c>
     </row>
+    <row r="146" ht="15">
+      <c r="B146" s="21" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B124:H124"/>
     <mergeCell ref="B125:H125"/>
     <mergeCell ref="B126:H126"/>
+    <mergeCell ref="B127:H127"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B122:I122"/>
-    <mergeCell ref="B123:H123"/>
+    <mergeCell ref="B123:I123"/>
+    <mergeCell ref="B124:H124"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
